--- a/main/ig/StructureDefinition-fr-lm-functional-status.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-functional-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-functional-status.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-functional-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-functional-status.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-functional-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-functional-status.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-functional-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-functional-status.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-functional-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -371,14 +371,14 @@
     <t>fr-lm-section.entry</t>
   </si>
   <si>
-    <t>fr-lm-functional-status.entry.assessments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-assessments
+    <t>fr-lm-functional-status.entry.assessment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-observation-assessment
 </t>
   </si>
   <si>
-    <t>Groupe de questionnaires d'évalutation</t>
+    <t>résultat d'une évaluation du statut fonctionnel</t>
   </si>
 </sst>
 </file>
@@ -693,7 +693,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="73.875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="77.953125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/main/ig/StructureDefinition-fr-lm-functional-status.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-functional-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-functional-status.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-functional-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
